--- a/artfynd/A 16223-2026 artfynd.xlsx
+++ b/artfynd/A 16223-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,335 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133999011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101356</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blåsippor, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>374300</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6616132</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>100 tals Blåsippor</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>rickard jakobsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>rickard jakobsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133999044</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58822</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granlåga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>374278</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6616123</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>rickard jakobsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>rickard jakobsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133998908</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96582</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granlåga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>374278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6616123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>6st observerade sporkapslar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>rickard jakobsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>rickard jakobsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16223-2026 artfynd.xlsx
+++ b/artfynd/A 16223-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133547607</v>
       </c>
       <c r="B2" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>133999011</v>
       </c>
       <c r="B3" t="n">
-        <v>101356</v>
+        <v>101376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåsippor, Vrm</t>
+          <t>Bytjärn, skogsdunge mittemot fågeltornet, Bytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -906,7 +906,7 @@
         <v>133999044</v>
       </c>
       <c r="B4" t="n">
-        <v>58822</v>
+        <v>58829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granlåga, Vrm</t>
+          <t>Bytjärn, skogsdunge mittemot fågeltornet, Bytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1013,7 +1013,7 @@
         <v>133998908</v>
       </c>
       <c r="B5" t="n">
-        <v>96582</v>
+        <v>96602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granlåga, Vrm</t>
+          <t>Bytjärn, skogsdunge mittemot fågeltornet, Bytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">

--- a/artfynd/A 16223-2026 artfynd.xlsx
+++ b/artfynd/A 16223-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133547607</v>
       </c>
       <c r="B2" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>133999011</v>
       </c>
       <c r="B3" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>133999044</v>
       </c>
       <c r="B4" t="n">
-        <v>58829</v>
+        <v>58839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>133998908</v>
       </c>
       <c r="B5" t="n">
-        <v>96602</v>
+        <v>96612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16223-2026 artfynd.xlsx
+++ b/artfynd/A 16223-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>133999011</v>
       </c>
       <c r="B3" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>133998908</v>
       </c>
       <c r="B5" t="n">
-        <v>96612</v>
+        <v>96614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16223-2026 artfynd.xlsx
+++ b/artfynd/A 16223-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>133999011</v>
       </c>
       <c r="B3" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>133998908</v>
       </c>
       <c r="B5" t="n">
-        <v>96615</v>
+        <v>96622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16223-2026 artfynd.xlsx
+++ b/artfynd/A 16223-2026 artfynd.xlsx
@@ -675,58 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133547607</v>
+        <v>133998908</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bytjärnen, Vrm</t>
+          <t>Bytjärn, skogsdunge mittemot fågeltornet, Bytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374301</v>
+        <v>374278</v>
       </c>
       <c r="R2" t="n">
-        <v>6616105</v>
+        <v>6616123</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6st observerade sporkapslar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,71 +767,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Carlzon</t>
+          <t>rickard jakobsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Carlzon</t>
+          <t>rickard jakobsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133999011</v>
+        <v>133547607</v>
       </c>
       <c r="B3" t="n">
-        <v>101396</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bytjärn, skogsdunge mittemot fågeltornet, Bytjärn, Vrm</t>
+          <t>Bytjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374300</v>
+        <v>374301</v>
       </c>
       <c r="R3" t="n">
-        <v>6616132</v>
+        <v>6616105</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,17 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>100 tals Blåsippor</t>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,19 +885,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>rickard jakobsson</t>
+          <t>Göran Carlzon</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>rickard jakobsson</t>
+          <t>Göran Carlzon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133998908</v>
+        <v>133999011</v>
       </c>
       <c r="B5" t="n">
-        <v>96622</v>
+        <v>101403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,26 +1021,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>374278</v>
+        <v>374300</v>
       </c>
       <c r="R5" t="n">
-        <v>6616123</v>
+        <v>6616132</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>6st observerade sporkapslar</t>
+          <t>100 tals Blåsippor</t>
         </is>
       </c>
       <c r="AD5" t="b">
